--- a/docs/StructureDefinition-blood-pressure-panel.xlsx
+++ b/docs/StructureDefinition-blood-pressure-panel.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-blood-pressure-panel.xlsx
+++ b/docs/StructureDefinition-blood-pressure-panel.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-blood-pressure-panel.xlsx
+++ b/docs/StructureDefinition-blood-pressure-panel.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="685">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>The position of the body when the observation was done, e.g. standing, sitting. To be used only when the body position in not precoordinated in the observation code.</t>
   </si>
   <si>
-    <t>Observation.extension:bodyPosition.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:bodyPosition.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -565,10 +569,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:bodyPosition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -806,10 +806,6 @@
   </si>
   <si>
     <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Observation.category:VSCat.extension</t>
@@ -3714,7 +3710,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3740,10 +3736,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3766,13 +3762,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3823,7 +3819,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3832,7 +3828,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3847,7 +3843,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3858,10 +3854,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3932,7 +3928,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3941,7 +3937,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3976,10 +3972,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4005,13 +4001,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -4061,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -4096,10 +4092,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4122,13 +4118,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4167,17 +4163,17 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4186,7 +4182,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4215,7 +4211,7 @@
         <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>178</v>
@@ -4240,13 +4236,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4295,7 +4291,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4304,7 +4300,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -5318,7 +5314,7 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>240</v>
@@ -5440,7 +5436,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>240</v>
@@ -5562,13 +5558,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5619,7 +5615,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5643,7 +5639,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5654,10 +5650,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5683,10 +5679,10 @@
         <v>138</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>197</v>
@@ -5730,7 +5726,7 @@
         <v>141</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
@@ -5739,7 +5735,7 @@
         <v>142</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5763,7 +5759,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5774,10 +5770,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5800,19 +5796,19 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5861,7 +5857,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5882,10 +5878,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5896,10 +5892,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5922,13 +5918,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5979,7 +5975,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6003,7 +5999,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -6014,10 +6010,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6043,10 +6039,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>197</v>
@@ -6090,7 +6086,7 @@
         <v>141</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -6099,7 +6095,7 @@
         <v>142</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6123,7 +6119,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6134,10 +6130,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6163,65 +6159,65 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6242,10 +6238,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6256,10 +6252,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6282,16 +6278,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6341,7 +6337,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6362,10 +6358,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6376,10 +6372,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6405,63 +6401,63 @@
         <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6482,10 +6478,10 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6496,10 +6492,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6522,17 +6518,17 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6581,7 +6577,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6602,10 +6598,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6616,10 +6612,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6642,19 +6638,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6703,7 +6699,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6724,10 +6720,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6738,10 +6734,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6764,19 +6760,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6825,7 +6821,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6846,10 +6842,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6860,14 +6856,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6886,19 +6882,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6908,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6926,11 +6922,11 @@
         <v>179</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6947,7 +6943,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>93</v>
@@ -6962,30 +6958,30 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7008,19 +7004,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -7069,7 +7065,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7084,19 +7080,19 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -7104,10 +7100,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7130,16 +7126,16 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7189,7 +7185,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7210,13 +7206,13 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -7224,14 +7220,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7250,19 +7246,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7311,7 +7307,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7326,19 +7322,19 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7346,14 +7342,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7372,19 +7368,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7433,7 +7429,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7442,25 +7438,25 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AK41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>20</v>
@@ -7468,10 +7464,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7494,16 +7490,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7553,7 +7549,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7574,13 +7570,13 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>20</v>
@@ -7588,10 +7584,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7614,17 +7610,17 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7673,7 +7669,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7688,19 +7684,19 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>20</v>
@@ -7708,10 +7704,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7734,19 +7730,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7795,7 +7791,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7804,7 +7800,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7813,27 +7809,27 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7856,19 +7852,19 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7896,37 +7892,37 @@
         <v>179</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI45" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7941,7 +7937,7 @@
         <v>136</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7952,14 +7948,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7978,19 +7974,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -8019,7 +8015,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -8037,7 +8033,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8055,27 +8051,27 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8098,19 +8094,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8159,7 +8155,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8180,10 +8176,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8194,10 +8190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8220,16 +8216,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8258,11 +8254,11 @@
         <v>179</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
       </c>
@@ -8279,7 +8275,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8297,27 +8293,27 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8340,19 +8336,19 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8380,11 +8376,11 @@
         <v>179</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
       </c>
@@ -8401,7 +8397,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8422,10 +8418,10 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8436,10 +8432,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8462,16 +8458,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8521,7 +8517,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8539,27 +8535,27 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8582,16 +8578,16 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8641,7 +8637,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8659,27 +8655,27 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8702,19 +8698,19 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8763,7 +8759,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8775,19 +8771,19 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8798,10 +8794,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8824,13 +8820,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8881,7 +8877,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8905,7 +8901,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8916,10 +8912,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8945,10 +8941,10 @@
         <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>197</v>
@@ -9001,7 +8997,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9025,7 +9021,7 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -9036,14 +9032,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9065,10 +9061,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>197</v>
@@ -9123,7 +9119,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9158,10 +9154,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9184,13 +9180,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9241,7 +9237,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9250,7 +9246,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9262,10 +9258,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9276,10 +9272,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9302,13 +9298,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9359,7 +9355,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9368,7 +9364,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9380,10 +9376,10 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9394,10 +9390,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9420,19 +9416,19 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9460,11 +9456,11 @@
         <v>117</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
       </c>
@@ -9481,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9499,13 +9495,13 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9516,10 +9512,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9542,19 +9538,19 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9579,14 +9575,14 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
       </c>
@@ -9603,7 +9599,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9621,13 +9617,13 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9638,10 +9634,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9664,17 +9660,17 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9723,7 +9719,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9747,7 +9743,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9758,10 +9754,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9784,13 +9780,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9841,7 +9837,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9862,10 +9858,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9876,10 +9872,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9902,16 +9898,16 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9961,7 +9957,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9982,10 +9978,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9996,10 +9992,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10022,16 +10018,16 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10081,7 +10077,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10102,10 +10098,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10116,10 +10112,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10142,19 +10138,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10191,7 +10187,7 @@
         <v>20</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
@@ -10201,7 +10197,7 @@
         <v>142</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10213,19 +10209,19 @@
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10236,10 +10232,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10262,13 +10258,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10319,7 +10315,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10343,7 +10339,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10354,10 +10350,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10383,10 +10379,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>197</v>
@@ -10439,7 +10435,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10463,7 +10459,7 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10474,14 +10470,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10503,10 +10499,10 @@
         <v>138</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>197</v>
@@ -10561,7 +10557,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10596,10 +10592,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10622,19 +10618,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10662,11 +10658,11 @@
         <v>179</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
       </c>
@@ -10683,7 +10679,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>93</v>
@@ -10701,16 +10697,16 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>20</v>
@@ -10718,10 +10714,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10744,19 +10740,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10784,37 +10780,37 @@
         <v>179</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10823,27 +10819,27 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10866,19 +10862,19 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="N70" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="O70" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10906,11 +10902,11 @@
         <v>179</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
       </c>
@@ -10927,7 +10923,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10936,7 +10932,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10951,7 +10947,7 @@
         <v>136</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10962,14 +10958,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10988,19 +10984,19 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -11028,11 +11024,11 @@
         <v>179</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
       </c>
@@ -11049,7 +11045,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11067,27 +11063,27 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11113,16 +11109,16 @@
         <v>20</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="N72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11171,7 +11167,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11192,10 +11188,10 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -11206,13 +11202,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C73" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>20</v>
@@ -11234,19 +11230,19 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11295,7 +11291,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11307,19 +11303,19 @@
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AK73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11330,10 +11326,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11356,13 +11352,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11413,7 +11409,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11437,7 +11433,7 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11448,10 +11444,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11477,10 +11473,10 @@
         <v>138</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>197</v>
@@ -11533,7 +11529,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11557,7 +11553,7 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11568,14 +11564,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11597,10 +11593,10 @@
         <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>197</v>
@@ -11655,7 +11651,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11690,10 +11686,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11716,19 +11712,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11738,7 +11734,7 @@
         <v>20</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>20</v>
@@ -11756,11 +11752,11 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
       </c>
@@ -11777,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>93</v>
@@ -11795,16 +11791,16 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>20</v>
@@ -11812,10 +11808,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11838,19 +11834,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O78" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11878,26 +11874,26 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11906,7 +11902,7 @@
         <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>105</v>
@@ -11915,30 +11911,30 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>20</v>
@@ -11960,19 +11956,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N79" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O79" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -12000,37 +11996,37 @@
         <v>179</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z79" t="s" s="2">
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI79" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>105</v>
@@ -12039,27 +12035,27 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12082,13 +12078,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12139,7 +12135,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12163,7 +12159,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12174,10 +12170,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12203,10 +12199,10 @@
         <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>197</v>
@@ -12250,7 +12246,7 @@
         <v>141</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>20</v>
@@ -12259,7 +12255,7 @@
         <v>142</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12283,7 +12279,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12294,10 +12290,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12320,19 +12316,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12381,7 +12377,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12402,10 +12398,10 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12416,10 +12412,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12445,20 +12441,20 @@
         <v>113</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q83" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q83" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="R83" t="s" s="2">
         <v>20</v>
@@ -12482,28 +12478,28 @@
         <v>232</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12524,10 +12520,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12538,10 +12534,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12564,17 +12560,17 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12623,7 +12619,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12644,10 +12640,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12658,10 +12654,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12687,72 +12683,72 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="S85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF85" t="s" s="2">
+      <c r="AG85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI85" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>105</v>
@@ -12764,10 +12760,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12778,10 +12774,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12807,65 +12803,65 @@
         <v>113</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12886,10 +12882,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12900,10 +12896,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12926,19 +12922,19 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="N87" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="O87" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12966,11 +12962,11 @@
         <v>179</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
       </c>
@@ -12987,7 +12983,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12996,7 +12992,7 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -13011,7 +13007,7 @@
         <v>136</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -13022,14 +13018,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13048,19 +13044,19 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -13088,11 +13084,11 @@
         <v>179</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
       </c>
@@ -13109,7 +13105,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13127,27 +13123,27 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13173,16 +13169,16 @@
         <v>20</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="N89" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -13231,7 +13227,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13252,10 +13248,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13266,13 +13262,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C90" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>20</v>
@@ -13294,19 +13290,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M90" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13355,7 +13351,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13367,19 +13363,19 @@
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AK90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13390,10 +13386,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13416,13 +13412,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13473,7 +13469,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13497,7 +13493,7 @@
         <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13508,10 +13504,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13537,10 +13533,10 @@
         <v>138</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>197</v>
@@ -13593,7 +13589,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13617,7 +13613,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13628,14 +13624,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13657,10 +13653,10 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>197</v>
@@ -13715,7 +13711,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13750,10 +13746,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13776,19 +13772,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13798,7 +13794,7 @@
         <v>20</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>20</v>
@@ -13816,11 +13812,11 @@
         <v>179</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
       </c>
@@ -13837,7 +13833,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>93</v>
@@ -13855,16 +13851,16 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>20</v>
@@ -13872,10 +13868,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13898,19 +13894,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13938,26 +13934,26 @@
         <v>179</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13966,7 +13962,7 @@
         <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13975,30 +13971,30 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>20</v>
@@ -14020,19 +14016,19 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -14060,37 +14056,37 @@
         <v>179</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z96" t="s" s="2">
+      <c r="AA96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI96" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>105</v>
@@ -14099,27 +14095,27 @@
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14142,13 +14138,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14199,7 +14195,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14223,7 +14219,7 @@
         <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14234,10 +14230,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14263,10 +14259,10 @@
         <v>138</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>197</v>
@@ -14310,7 +14306,7 @@
         <v>141</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>20</v>
@@ -14319,7 +14315,7 @@
         <v>142</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14343,7 +14339,7 @@
         <v>20</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14354,10 +14350,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14380,19 +14376,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14441,7 +14437,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14462,10 +14458,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14476,10 +14472,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14505,20 +14501,20 @@
         <v>113</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q100" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q100" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="R100" t="s" s="2">
         <v>20</v>
@@ -14542,28 +14538,28 @@
         <v>232</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14584,10 +14580,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14598,10 +14594,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14624,17 +14620,17 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14683,7 +14679,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14704,10 +14700,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14718,10 +14714,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14747,72 +14743,72 @@
         <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="S102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF102" t="s" s="2">
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI102" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14824,10 +14820,10 @@
         <v>20</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
@@ -14838,10 +14834,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14867,65 +14863,65 @@
         <v>113</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14946,10 +14942,10 @@
         <v>20</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>20</v>
@@ -14960,10 +14956,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14986,19 +14982,19 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="N104" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="O104" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -15026,11 +15022,11 @@
         <v>179</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z104" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
       </c>
@@ -15047,7 +15043,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15056,7 +15052,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15071,7 +15067,7 @@
         <v>136</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
@@ -15082,14 +15078,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15108,19 +15104,19 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
@@ -15148,11 +15144,11 @@
         <v>179</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>20</v>
       </c>
@@ -15169,7 +15165,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15187,27 +15183,27 @@
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM105" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AN105" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP105" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15233,16 +15229,16 @@
         <v>20</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M106" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="N106" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O106" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>20</v>
@@ -15291,7 +15287,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15312,10 +15308,10 @@
         <v>20</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>20</v>
@@ -15326,13 +15322,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>20</v>
@@ -15354,19 +15350,19 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -15415,7 +15411,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15427,19 +15423,19 @@
         <v>20</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AK107" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>20</v>
@@ -15450,10 +15446,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15476,13 +15472,13 @@
         <v>20</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15533,7 +15529,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15557,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>20</v>
@@ -15568,10 +15564,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15597,10 +15593,10 @@
         <v>138</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>197</v>
@@ -15653,7 +15649,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15677,7 +15673,7 @@
         <v>20</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>20</v>
@@ -15688,14 +15684,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15717,10 +15713,10 @@
         <v>138</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>197</v>
@@ -15775,7 +15771,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15810,10 +15806,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15836,19 +15832,19 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15858,7 +15854,7 @@
         <v>20</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>20</v>
@@ -15876,11 +15872,11 @@
         <v>179</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
       </c>
@@ -15897,7 +15893,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>93</v>
@@ -15915,16 +15911,16 @@
         <v>20</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN111" t="s" s="2">
+      <c r="AO111" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>20</v>
@@ -15932,10 +15928,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15958,19 +15954,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N112" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O112" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15998,26 +15994,26 @@
         <v>179</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC112" s="2"/>
       <c r="AD112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16026,7 +16022,7 @@
         <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -16035,30 +16031,30 @@
         <v>20</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>20</v>
@@ -16080,19 +16076,19 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="O113" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -16120,37 +16116,37 @@
         <v>179</v>
       </c>
       <c r="Y113" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z113" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z113" t="s" s="2">
+      <c r="AA113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI113" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16159,27 +16155,27 @@
         <v>20</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AO113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP113" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16202,13 +16198,13 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16259,7 +16255,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16283,7 +16279,7 @@
         <v>20</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>20</v>
@@ -16294,10 +16290,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16323,10 +16319,10 @@
         <v>138</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>197</v>
@@ -16370,7 +16366,7 @@
         <v>141</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>20</v>
@@ -16379,7 +16375,7 @@
         <v>142</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16403,7 +16399,7 @@
         <v>20</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>20</v>
@@ -16414,10 +16410,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16440,19 +16436,19 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -16501,7 +16497,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16522,10 +16518,10 @@
         <v>20</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>20</v>
@@ -16536,10 +16532,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16565,20 +16561,20 @@
         <v>113</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q117" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q117" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="R117" t="s" s="2">
         <v>20</v>
@@ -16602,28 +16598,28 @@
         <v>232</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z117" t="s" s="2">
+      <c r="AA117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16644,10 +16640,10 @@
         <v>20</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>20</v>
@@ -16658,10 +16654,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16684,17 +16680,17 @@
         <v>94</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -16743,7 +16739,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16764,10 +16760,10 @@
         <v>20</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>20</v>
@@ -16778,10 +16774,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16807,72 +16803,72 @@
         <v>107</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF119" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="S119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF119" t="s" s="2">
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI119" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>105</v>
@@ -16884,10 +16880,10 @@
         <v>20</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>20</v>
@@ -16898,10 +16894,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16927,65 +16923,65 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17006,10 +17002,10 @@
         <v>20</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>20</v>
@@ -17020,10 +17016,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17046,19 +17042,19 @@
         <v>20</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="N121" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="O121" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>20</v>
@@ -17086,11 +17082,11 @@
         <v>179</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z121" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA121" t="s" s="2">
         <v>20</v>
       </c>
@@ -17107,7 +17103,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17116,7 +17112,7 @@
         <v>93</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>105</v>
@@ -17131,7 +17127,7 @@
         <v>136</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>20</v>
@@ -17142,14 +17138,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17168,19 +17164,19 @@
         <v>20</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -17208,11 +17204,11 @@
         <v>179</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>20</v>
       </c>
@@ -17229,7 +17225,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17247,27 +17243,27 @@
         <v>20</v>
       </c>
       <c r="AL122" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM122" t="s" s="2">
+      <c r="AN122" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP122" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17293,16 +17289,16 @@
         <v>20</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M123" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="N123" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -17351,7 +17347,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17372,10 +17368,10 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-blood-pressure-panel.xlsx
+++ b/docs/StructureDefinition-blood-pressure-panel.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
